--- a/data/LiPF6_data.xlsx
+++ b/data/LiPF6_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yassir.lamaachi\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yassir.lamaachi\Desktop\On the job two SPS\SPS Python Dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB1C73A-D6A4-413B-9B44-B065E871F5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33ED4D0-4310-471E-BFF1-BFF25E30FF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="440" yWindow="400" windowWidth="18580" windowHeight="9050" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Companies" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="293">
   <si>
     <t>Company</t>
   </si>
@@ -62,141 +62,48 @@
     <t>China</t>
   </si>
   <si>
-    <t>Guangzhou, Guangdong</t>
-  </si>
-  <si>
-    <t>CATL, BYD</t>
-  </si>
-  <si>
-    <t>Integrated electrolyte chain</t>
-  </si>
-  <si>
     <t>Industrial Scale</t>
   </si>
   <si>
     <t>Do-Fluoride (DFD)</t>
   </si>
   <si>
-    <t>Jiaozuo, Henan</t>
-  </si>
-  <si>
-    <t>BYD, Soulbrain, Mitsubishi</t>
-  </si>
-  <si>
-    <t>Crystalline LiPF6 via PCl3 process</t>
-  </si>
-  <si>
     <t>Zhuhai Tonze (Xintai/Taiji)</t>
   </si>
   <si>
-    <t>Zhuhai, Guangdong</t>
-  </si>
-  <si>
-    <t>Domestic China</t>
-  </si>
-  <si>
-    <t>Solution-based LiPF6 production</t>
-  </si>
-  <si>
     <t>Guangdong STA</t>
   </si>
   <si>
-    <t>Shenzhen, Guangdong</t>
-  </si>
-  <si>
-    <t>New entrant, no output yet</t>
-  </si>
-  <si>
     <t>Pilot Project</t>
   </si>
   <si>
     <t>Zhejiang Yongtai (YONTA)</t>
   </si>
   <si>
-    <t>Taizhou, Zhejiang</t>
-  </si>
-  <si>
-    <t>China EV sector</t>
-  </si>
-  <si>
-    <t>LiFSI &amp; LiPF6 mix; solution ramp-up</t>
-  </si>
-  <si>
     <t>Jiangsu Jiujiu (99 Technology)</t>
   </si>
   <si>
-    <t>Zhenjiang, Jiangsu</t>
-  </si>
-  <si>
-    <t>BYD, Enchem, Capchem</t>
-  </si>
-  <si>
-    <t>Battery-grade LiPF6 scaling up</t>
-  </si>
-  <si>
     <t>Tianjin Jinniu Power</t>
   </si>
   <si>
-    <t>Tianjin</t>
-  </si>
-  <si>
-    <t>Local China</t>
-  </si>
-  <si>
-    <t>Formulates electrolyte blends</t>
-  </si>
-  <si>
     <t>Morita Chemical (Morita New Energy)</t>
   </si>
   <si>
     <t>Japan</t>
   </si>
   <si>
-    <t>Fukushima</t>
-  </si>
-  <si>
-    <t>Panasonic, Japanese OEMs</t>
-  </si>
-  <si>
-    <t>Japan-China JV; 99.9% purity</t>
-  </si>
-  <si>
     <t>Central Glass</t>
   </si>
   <si>
-    <t>Ube, Yamaguchi</t>
-  </si>
-  <si>
-    <t>Toyota, Panasonic</t>
-  </si>
-  <si>
-    <t>High-purity concentrate technology</t>
-  </si>
-  <si>
     <t>Stella Chemifa</t>
   </si>
   <si>
     <t>Osaka</t>
   </si>
   <si>
-    <t>Japan battery makers</t>
-  </si>
-  <si>
-    <t>Fluorine-based additives</t>
-  </si>
-  <si>
     <t>Kanto Denka Kogyo</t>
   </si>
   <si>
-    <t>Tokyo</t>
-  </si>
-  <si>
-    <t>Panasonic</t>
-  </si>
-  <si>
-    <t>Legacy LiPF6 producer</t>
-  </si>
-  <si>
     <t>Foosung</t>
   </si>
   <si>
@@ -206,57 +113,21 @@
     <t>Ulsan</t>
   </si>
   <si>
-    <t>BASF JV</t>
-  </si>
-  <si>
-    <t>HF-Li salt integrated production</t>
-  </si>
-  <si>
     <t>Soulbrain (S6F New Energy JV)</t>
   </si>
   <si>
-    <t>Seoul</t>
-  </si>
-  <si>
-    <t>Soulbrain</t>
-  </si>
-  <si>
-    <t>New Korean JV with Do-Fluoride</t>
-  </si>
-  <si>
-    <t>Upcoming Facility</t>
-  </si>
-  <si>
     <t>Formosa Plastics</t>
   </si>
   <si>
     <t>Taiwan</t>
   </si>
   <si>
-    <t>Mailiao, Yunlin</t>
-  </si>
-  <si>
-    <t>Formosa internal</t>
-  </si>
-  <si>
-    <t>Petrochemicals to LiPF6 expansion</t>
-  </si>
-  <si>
     <t>Orbia (Koura)</t>
   </si>
   <si>
-    <t>United States</t>
-  </si>
-  <si>
     <t>St. Gabriel, Louisiana</t>
   </si>
   <si>
-    <t>GM, Ford-SK</t>
-  </si>
-  <si>
-    <t>First U.S. LiPF6 plant</t>
-  </si>
-  <si>
     <t>Gujarat Fluorochem (GFCL EV)</t>
   </si>
   <si>
@@ -264,12 +135,6 @@
   </si>
   <si>
     <t>Dahej, Gujarat</t>
-  </si>
-  <si>
-    <t>Indian battery makers</t>
-  </si>
-  <si>
-    <t>India’s first LiPF6 producer</t>
   </si>
   <si>
     <t>Reference</t>
@@ -1577,6 +1442,417 @@
   <si>
     <t>Comment</t>
   </si>
+  <si>
+    <t>Sources</t>
+  </si>
+  <si>
+    <t>Guangzhou Tinci Materials Technology Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Guangzhou, Guangdong, China</t>
+  </si>
+  <si>
+    <t>BYD and other domestic EV battery makers</t>
+  </si>
+  <si>
+    <t>Organic solvent process for LiPF₆</t>
+  </si>
+  <si>
+    <t>23.1300</t>
+  </si>
+  <si>
+    <t>113.2600</t>
+  </si>
+  <si>
+    <t>https://www.avicenne.com/download/lipf6-demand-pricing.pdf</t>
+  </si>
+  <si>
+    <t>Do-Fluoride (DFD) New Materials Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Jiaozuo, Henan, China</t>
+  </si>
+  <si>
+    <t>Domestic battery manufacturers (e.g. CATL)</t>
+  </si>
+  <si>
+    <t>Crystalline LiPF₆ via Li₂CO₃ + HF + PCl₃</t>
+  </si>
+  <si>
+    <t>35.2400</t>
+  </si>
+  <si>
+    <t>113.2300</t>
+  </si>
+  <si>
+    <t>https://dfdchem.com/announcement/capacity-plan-2024</t>
+  </si>
+  <si>
+    <t>Guangdong Tonze Electric Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Ruichang, Jiangxi, China</t>
+  </si>
+  <si>
+    <t>BYD (supply of up to 11300 t)</t>
+  </si>
+  <si>
+    <t>Conventional LiPF₆ production</t>
+  </si>
+  <si>
+    <t>29.2600</t>
+  </si>
+  <si>
+    <t>115.6700</t>
+  </si>
+  <si>
+    <t>https://www.tonze.cn/investor/news-july-2023</t>
+  </si>
+  <si>
+    <t>Zhejiang Yongtai Technology Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Taizhou, Zhejiang, China</t>
+  </si>
+  <si>
+    <t>CATL (multi-year contract)</t>
+  </si>
+  <si>
+    <t>Fluorochemical integration</t>
+  </si>
+  <si>
+    <t>28.6600</t>
+  </si>
+  <si>
+    <t>121.4400</t>
+  </si>
+  <si>
+    <t>https://www.yongtaitech.com/li-salt-expansion</t>
+  </si>
+  <si>
+    <t>Shenzhen Sunxing Light Alloys (STA)</t>
+  </si>
+  <si>
+    <t>Shenzhen, Guangdong, China</t>
+  </si>
+  <si>
+    <t>New entrant; pilot phase</t>
+  </si>
+  <si>
+    <t>22.5400</t>
+  </si>
+  <si>
+    <t>114.0500</t>
+  </si>
+  <si>
+    <t>https://www.cnal.com/news/sunxing-pilot-2023</t>
+  </si>
+  <si>
+    <t>Yan’an Bicon Pharmaceutical Co.</t>
+  </si>
+  <si>
+    <t>Yan’an, Shaanxi, China</t>
+  </si>
+  <si>
+    <t>BYD (3360 t contract)</t>
+  </si>
+  <si>
+    <t>Fluorochemical via Jijiu subsidiary</t>
+  </si>
+  <si>
+    <t>36.6000</t>
+  </si>
+  <si>
+    <t>109.4900</t>
+  </si>
+  <si>
+    <t>https://www.bicon.com.cn/en/news/expansion</t>
+  </si>
+  <si>
+    <t>Morita New Energy (Zhangjiagang) Co., Ltd.</t>
+  </si>
+  <si>
+    <t>China (Japan JV)</t>
+  </si>
+  <si>
+    <t>Zhangjiagang, Jiangsu</t>
+  </si>
+  <si>
+    <t>Japanese and Chinese OEMs</t>
+  </si>
+  <si>
+    <t>Morita Japanese LiPF₆ process</t>
+  </si>
+  <si>
+    <t>31.9700</t>
+  </si>
+  <si>
+    <t>120.5400</t>
+  </si>
+  <si>
+    <t>https://www.morita-chem.co.jp/lipf6</t>
+  </si>
+  <si>
+    <t>Sichuan Huangming Lithium Energy</t>
+  </si>
+  <si>
+    <t>Dujiangyan, Sichuan</t>
+  </si>
+  <si>
+    <t>30.9900</t>
+  </si>
+  <si>
+    <t>103.6500</t>
+  </si>
+  <si>
+    <t>https://www.chinalithium.com/huangming-announcement</t>
+  </si>
+  <si>
+    <t>Anhui Meisenbao Tech Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Huaibei, Anhui</t>
+  </si>
+  <si>
+    <t>General battery chemicals</t>
+  </si>
+  <si>
+    <t>33.9744</t>
+  </si>
+  <si>
+    <t>116.7917</t>
+  </si>
+  <si>
+    <t>https://www.meisenbao.com</t>
+  </si>
+  <si>
+    <t>Formosa Mitsui Advanced Chemicals</t>
+  </si>
+  <si>
+    <t>Taipei (prod. in CN + TW)</t>
+  </si>
+  <si>
+    <t>Asian battery makers</t>
+  </si>
+  <si>
+    <t>Mitsui-licensed electrolyte process</t>
+  </si>
+  <si>
+    <t>25.0330</t>
+  </si>
+  <si>
+    <t>121.5654</t>
+  </si>
+  <si>
+    <t>https://www.fmchem.com.tw</t>
+  </si>
+  <si>
+    <t>Kanto Denka Kogyo Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Chiyoda, Tokyo</t>
+  </si>
+  <si>
+    <t>Licensor to Orbia USA</t>
+  </si>
+  <si>
+    <t>Japanese LiPF₆ technology</t>
+  </si>
+  <si>
+    <t>35.6900</t>
+  </si>
+  <si>
+    <t>139.7700</t>
+  </si>
+  <si>
+    <t>https://www.kantodenka.co.jp/english/products/lipf6</t>
+  </si>
+  <si>
+    <t>Stella Chemifa Corporation</t>
+  </si>
+  <si>
+    <t>Fluoride specialty materials</t>
+  </si>
+  <si>
+    <t>34.6937</t>
+  </si>
+  <si>
+    <t>135.5023</t>
+  </si>
+  <si>
+    <t>Central Glass Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Urayasu, Chiba</t>
+  </si>
+  <si>
+    <t>Panasonic, others</t>
+  </si>
+  <si>
+    <t>Electrolyte production, imports LiPF₆</t>
+  </si>
+  <si>
+    <t>35.6700</t>
+  </si>
+  <si>
+    <t>139.8900</t>
+  </si>
+  <si>
+    <t>MU Ionic Solutions (Mitsubishi &amp; UBE)</t>
+  </si>
+  <si>
+    <t>Tokyo (global)</t>
+  </si>
+  <si>
+    <t>Global cell makers</t>
+  </si>
+  <si>
+    <t>Proprietary MUIS electrolyte mixing</t>
+  </si>
+  <si>
+    <t>https://www.muis.co.jp/news/licensing-2023</t>
+  </si>
+  <si>
+    <t>Foosung Co., Ltd.</t>
+  </si>
+  <si>
+    <t>LG, Samsung SDI</t>
+  </si>
+  <si>
+    <t>High-purity LiPF₆ pioneer</t>
+  </si>
+  <si>
+    <t>35.5383</t>
+  </si>
+  <si>
+    <t>129.3114</t>
+  </si>
+  <si>
+    <t>Soulbrain Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Seongnam</t>
+  </si>
+  <si>
+    <t>LG, Samsung, SK</t>
+  </si>
+  <si>
+    <t>Electrolyte producer (uses LiPF₆)</t>
+  </si>
+  <si>
+    <t>37.3665</t>
+  </si>
+  <si>
+    <t>127.1069</t>
+  </si>
+  <si>
+    <t>https://www.soulbrain.co.kr</t>
+  </si>
+  <si>
+    <t>Neogen Chemicals Ltd.</t>
+  </si>
+  <si>
+    <t>Future Indian OEMs</t>
+  </si>
+  <si>
+    <t>Licensed from MUIS (Japan)</t>
+  </si>
+  <si>
+    <t>21.7080</t>
+  </si>
+  <si>
+    <t>72.6000</t>
+  </si>
+  <si>
+    <t>https://www.neogenchem.com/press</t>
+  </si>
+  <si>
+    <t>Gujarat Fluorochemicals Ltd.</t>
+  </si>
+  <si>
+    <t>Indian battery ecosystem</t>
+  </si>
+  <si>
+    <t>LiPF₆ + LFP via fluorine chemistry</t>
+  </si>
+  <si>
+    <t>https://www.gflltd.com</t>
+  </si>
+  <si>
+    <t>Orbia (Koura Fluorochemicals)</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Licensed from Kanto Denka (Japan)</t>
+  </si>
+  <si>
+    <t>30.2560</t>
+  </si>
+  <si>
+    <t>-91.1010</t>
+  </si>
+  <si>
+    <t>https://www.orbia.com/projects/koura-lipf6</t>
+  </si>
+  <si>
+    <t>Capchem Technology</t>
+  </si>
+  <si>
+    <t>Shenzhen + Poland</t>
+  </si>
+  <si>
+    <t>Tesla, Panasonic, BYD</t>
+  </si>
+  <si>
+    <t>Integrated electrolyte production</t>
+  </si>
+  <si>
+    <t>https://www.capchem.com</t>
+  </si>
+  <si>
+    <t>Guotai Huarong</t>
+  </si>
+  <si>
+    <t>LG, CATL, Panasonic</t>
+  </si>
+  <si>
+    <t>Electrolytes (top-3 globally)</t>
+  </si>
+  <si>
+    <t>https://www.gthr.com.cn</t>
+  </si>
+  <si>
+    <t>Iolitec GmbH</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Heilbronn</t>
+  </si>
+  <si>
+    <t>EU niche market</t>
+  </si>
+  <si>
+    <t>Ionic liquids + LiPF₆ blends</t>
+  </si>
+  <si>
+    <t>49.1400</t>
+  </si>
+  <si>
+    <t>9.2200</t>
+  </si>
+  <si>
+    <t>https://www.iolitec.de</t>
+  </si>
+  <si>
+    <t>(planned US OEMs)</t>
+  </si>
+  <si>
+    <t>Upcoming Facility</t>
+  </si>
 </sst>
 </file>
 
@@ -1667,7 +1943,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1679,6 +1955,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1985,551 +2267,842 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="55.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="K1" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>23.130196399999999</v>
-      </c>
-      <c r="H2">
-        <v>113.2592945</v>
-      </c>
-      <c r="I2">
-        <v>62</v>
-      </c>
-      <c r="J2">
+      <c r="G2" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="I2" s="6">
+        <v>62000</v>
+      </c>
+      <c r="J2" s="6">
+        <v>10000</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I3" s="6">
+        <v>55000</v>
+      </c>
+      <c r="J3" s="6">
+        <v>50000</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="I4" s="6">
+        <v>18160</v>
+      </c>
+      <c r="J4" s="6">
+        <v>30000</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I5" s="6">
+        <v>8000</v>
+      </c>
+      <c r="J5" s="6">
+        <v>67000</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="I6" s="6">
+        <v>800</v>
+      </c>
+      <c r="J6" s="6">
+        <v>15000</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="I7" s="6">
+        <v>6400</v>
+      </c>
+      <c r="J7" s="6">
+        <v>40000</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="I8" s="6">
+        <v>3000</v>
+      </c>
+      <c r="J8" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="K8" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6">
+        <v>10000</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I15" s="6">
+        <v>0</v>
+      </c>
+      <c r="J15" s="6">
+        <v>30000</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I17" s="6">
+        <v>0</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I18" s="6">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6">
+        <v>30000</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I19" s="6">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6">
+        <v>20000</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="I20" s="6">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6">
+        <v>10000</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="I21" s="6">
+        <v>65000</v>
+      </c>
+      <c r="J21" s="6">
+        <v>140000</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="I22" s="6">
+        <v>70000</v>
+      </c>
+      <c r="J22" s="6">
+        <v>40000</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F23" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>35.137500000000003</v>
-      </c>
-      <c r="H3">
-        <v>113.143889</v>
-      </c>
-      <c r="I3">
-        <v>55</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4">
-        <v>22.273734000000001</v>
-      </c>
-      <c r="H4">
-        <v>113.5721327</v>
-      </c>
-      <c r="I4">
-        <v>18</v>
-      </c>
-      <c r="J4">
+      <c r="G23" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="I23" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5">
-        <v>22.544574099999998</v>
-      </c>
-      <c r="H5">
-        <v>114.0545429</v>
-      </c>
-      <c r="I5">
+      <c r="J23" s="6">
         <v>0</v>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6">
-        <v>28.6581723</v>
-      </c>
-      <c r="H6">
-        <v>121.41638759999999</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>32.189195900000001</v>
-      </c>
-      <c r="H7">
-        <v>119.4200069</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8">
-        <v>39.303261900000003</v>
-      </c>
-      <c r="H8">
-        <v>117.4163641</v>
-      </c>
-      <c r="I8">
-        <v>4</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9">
-        <v>37.760776999999997</v>
-      </c>
-      <c r="H9">
-        <v>140.47458069999999</v>
-      </c>
-      <c r="I9">
-        <v>3</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10">
-        <v>33.951849799999998</v>
-      </c>
-      <c r="H10">
-        <v>131.2472243</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11">
-        <v>34.693756899999997</v>
-      </c>
-      <c r="H11">
-        <v>135.5014539</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12">
-        <v>35.676860099999999</v>
-      </c>
-      <c r="H12">
-        <v>139.76389470000001</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13">
-        <v>35.539169700000002</v>
-      </c>
-      <c r="H13">
-        <v>129.3119136</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14">
-        <v>37.566679100000002</v>
-      </c>
-      <c r="H14">
-        <v>126.9782914</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15">
-        <v>23.753841000000001</v>
-      </c>
-      <c r="H15">
-        <v>120.252043</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>72</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16">
-        <v>30.257695300000002</v>
-      </c>
-      <c r="H16">
-        <v>-91.099270599999997</v>
-      </c>
-      <c r="I16">
-        <v>10</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17">
-        <v>21.709301</v>
-      </c>
-      <c r="H17">
-        <v>72.589396300000004</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
+      <c r="K23" s="2" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{CEE88878-870E-4974-A2B7-70753B279E32}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{47B1374C-F153-4BE5-BDB3-E5D364686200}"/>
+    <hyperlink ref="K4" r:id="rId3" xr:uid="{80E831D0-12C1-429D-9DB3-51F1F6B2B3B6}"/>
+    <hyperlink ref="K5" r:id="rId4" xr:uid="{0ECCC3D4-28CE-4E38-A00C-F49E9EF7092B}"/>
+    <hyperlink ref="K6" r:id="rId5" xr:uid="{98EF04C6-31F4-479D-8EA6-735021231FE7}"/>
+    <hyperlink ref="K7" r:id="rId6" xr:uid="{DE3BC8BE-FF97-4A58-A448-30AEF0ECC9CB}"/>
+    <hyperlink ref="K8" r:id="rId7" xr:uid="{F069234E-431D-4A63-B8C3-95AECAB81FB5}"/>
+    <hyperlink ref="K9" r:id="rId8" xr:uid="{7F8481E5-4915-46A6-90AD-C5817DC25557}"/>
+    <hyperlink ref="K10" r:id="rId9" display="https://www.meisenbao.com/" xr:uid="{FA9A05E1-02A7-4792-A9FD-94C053D6A3CD}"/>
+    <hyperlink ref="K11" r:id="rId10" display="https://www.fmchem.com.tw/" xr:uid="{DC8BCE4F-5C1E-493A-B58E-DF2DF534DA64}"/>
+    <hyperlink ref="K12" r:id="rId11" xr:uid="{67105CD3-F4A1-4F1F-972B-4EC8578710BB}"/>
+    <hyperlink ref="K13" r:id="rId12" display="https://www.stella-chemifa.co.jp/" xr:uid="{66901FBE-556B-45E9-B2DE-8C2687A77308}"/>
+    <hyperlink ref="K14" r:id="rId13" display="https://www.cgco.co.jp/" xr:uid="{B4D633B3-343E-4890-B512-316444C69515}"/>
+    <hyperlink ref="K15" r:id="rId14" xr:uid="{687E9E47-63BD-4885-8DFE-C4E782C40E4A}"/>
+    <hyperlink ref="K16" r:id="rId15" display="https://www.foosung.com/" xr:uid="{75BBEDAF-C681-4FD8-AD45-7CB270B72680}"/>
+    <hyperlink ref="K17" r:id="rId16" display="https://www.soulbrain.co.kr/" xr:uid="{E8A7A1A6-26BE-46C7-BCDD-E8B4B75A1B09}"/>
+    <hyperlink ref="K18" r:id="rId17" xr:uid="{46DA3986-0F2B-4779-8A55-C993CD449F52}"/>
+    <hyperlink ref="K19" r:id="rId18" display="https://www.gflltd.com/" xr:uid="{85C9EE62-1132-4414-852C-8CE94083DCD1}"/>
+    <hyperlink ref="K20" r:id="rId19" xr:uid="{B6AF5653-57DE-4C8D-8583-0BC1A405017E}"/>
+    <hyperlink ref="K21" r:id="rId20" display="https://www.capchem.com/" xr:uid="{AC1527C4-A87B-4A36-BFEC-C20B8CB3A4B1}"/>
+    <hyperlink ref="K22" r:id="rId21" display="https://www.gthr.com.cn/" xr:uid="{5A723C59-5AB1-425B-A7E6-7F0FF66D4EA3}"/>
+    <hyperlink ref="K23" r:id="rId22" display="https://www.iolitec.de/" xr:uid="{193E0300-6F77-4A30-B859-9BBFF0408691}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2544,10 +3117,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -2555,175 +3128,175 @@
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
         <v>49</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2756,43 +3329,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -2800,40 +3373,40 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="F2" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="I2" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="J2" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="K2" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="L2" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="M2" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -2841,40 +3414,40 @@
         <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="G3" t="s">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="J3" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="K3" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="L3" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="M3" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -2882,40 +3455,40 @@
         <v>125</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="F4" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="G4" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="H4" t="s">
-        <v>147</v>
+        <v>102</v>
       </c>
       <c r="I4" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="J4" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="K4" t="s">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="L4" t="s">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="M4" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -2923,40 +3496,40 @@
         <v>127</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>154</v>
+        <v>109</v>
       </c>
       <c r="F5" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="G5" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="H5" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="I5" t="s">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="J5" t="s">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="K5" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="L5" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="M5" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -2964,40 +3537,40 @@
         <v>166</v>
       </c>
       <c r="B6" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" t="s">
+        <v>121</v>
+      </c>
+      <c r="J6" t="s">
         <v>122</v>
       </c>
-      <c r="E6" t="s">
-        <v>162</v>
-      </c>
-      <c r="F6" t="s">
-        <v>163</v>
-      </c>
-      <c r="G6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H6" t="s">
-        <v>165</v>
-      </c>
-      <c r="I6" t="s">
-        <v>166</v>
-      </c>
-      <c r="J6" t="s">
-        <v>167</v>
-      </c>
       <c r="K6" t="s">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="L6" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="M6" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -3005,40 +3578,40 @@
         <v>167</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>124</v>
       </c>
       <c r="C7" t="s">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="F7" t="s">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="G7" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
       <c r="H7" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="I7" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="J7" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="K7" t="s">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="L7" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="M7" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -3046,40 +3619,40 @@
         <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="F8" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="G8" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="H8" t="s">
-        <v>181</v>
+        <v>136</v>
       </c>
       <c r="I8" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="J8" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="K8" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="L8" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="M8" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3094,24 +3667,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>186</v>
+        <v>141</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>187</v>
+        <v>142</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="D2" s="4">
         <v>45741.198063668977</v>
@@ -3119,10 +3692,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>147</v>
       </c>
       <c r="D3" s="4">
         <v>45741.467341701391</v>
@@ -3130,10 +3703,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>194</v>
+        <v>149</v>
       </c>
       <c r="D4" s="4">
         <v>45748.87497996528</v>
@@ -3141,10 +3714,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="D5" s="4">
         <v>45748.878286446758</v>
@@ -3166,16 +3739,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
